--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -86,7 +86,7 @@
     <x:t>Period Covered:</x:t>
   </x:si>
   <x:si>
-    <x:t>0 Years</x:t>
+    <x:t>1 Year</x:t>
   </x:si>
   <x:si>
     <x:t>No. of Years</x:t>
@@ -1775,7 +1775,7 @@
       <x:c r="A9" s="17" t="s"/>
       <x:c r="B9" s="17" t="s"/>
       <x:c r="C9" s="17" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="18" t="s">
         <x:v>10</x:v>
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>1</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>8</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>0</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>1</x:v>
+        <x:v>3001</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>0</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>181</x:v>
+        <x:v>841</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>218</x:v>
+        <x:v>5058</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>841</x:v>
+        <x:v>1201</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>151</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>5058</x:v>
+        <x:v>5478</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>1201</x:v>
+        <x:v>841</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>211</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>5478</x:v>
+        <x:v>5058</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>3001</x:v>
+        <x:v>4501</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>151</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>5058</x:v>
+        <x:v>6588</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>510</x:v>
+        <x:v>1010</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>4501</x:v>
+        <x:v>6001</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>510</x:v>
+        <x:v>1010</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>181</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>6588</x:v>
+        <x:v>9118</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>1010</x:v>
+        <x:v>2010</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>6001</x:v>
+        <x:v>9001</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>1010</x:v>
+        <x:v>2010</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>211</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>9118</x:v>
+        <x:v>14178</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>9001</x:v>
+        <x:v>10501</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>271</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>14178</x:v>
+        <x:v>15708</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>0</x:v>
+        <x:v>3380</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>2010</x:v>
+        <x:v>7410</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>2010</x:v>
+        <x:v>7410</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>1</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>301</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>15708</x:v>
+        <x:v>30058</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>3380</x:v>
+        <x:v>3476</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7410</x:v>
+        <x:v>7590</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7410</x:v>
+        <x:v>7590</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>421</x:v>
+        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>30058</x:v>
+        <x:v>30544</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7590</x:v>
+        <x:v>7770</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7590</x:v>
+        <x:v>7770</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>451</x:v>
+        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>30544</x:v>
+        <x:v>30934</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7770</x:v>
+        <x:v>9570</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>10501</x:v>
+        <x:v>12001</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7770</x:v>
+        <x:v>9570</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>481</x:v>
+        <x:v>541</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>30934</x:v>
+        <x:v>36094</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>3476</x:v>
+        <x:v>4436</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>9570</x:v>
+        <x:v>11370</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>12001</x:v>
+        <x:v>13501</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>9570</x:v>
+        <x:v>11370</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>541</x:v>
+        <x:v>601</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>36094</x:v>
+        <x:v>42214</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>13501</x:v>
+        <x:v>15721</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>601</x:v>
+        <x:v>661</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>42214</x:v>
+        <x:v>44494</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>15721</x:v>
+        <x:v>17941</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>661</x:v>
+        <x:v>721</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>44494</x:v>
+        <x:v>46774</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>17941</x:v>
+        <x:v>25381</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>721</x:v>
+        <x:v>901</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>46774</x:v>
+        <x:v>54394</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>11370</x:v>
+        <x:v>11550</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>25381</x:v>
+        <x:v>27541</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>11370</x:v>
+        <x:v>11550</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>901</x:v>
+        <x:v>961</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>54394</x:v>
+        <x:v>56974</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>27541</x:v>
+        <x:v>29041</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>961</x:v>
+        <x:v>991</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>56974</x:v>
+        <x:v>58504</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>11550</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>29041</x:v>
+        <x:v>30541</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>11550</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>991</x:v>
+        <x:v>1021</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>58504</x:v>
+        <x:v>61034</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>12050</x:v>
+        <x:v>12230</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>30541</x:v>
+        <x:v>31261</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>12050</x:v>
+        <x:v>12230</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1021</x:v>
+        <x:v>1051</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>61034</x:v>
+        <x:v>62144</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>31261</x:v>
+        <x:v>32761</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1051</x:v>
+        <x:v>1081</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>62144</x:v>
+        <x:v>63674</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>12230</x:v>
+        <x:v>13230</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>32761</x:v>
+        <x:v>38701</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>12230</x:v>
+        <x:v>13230</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1081</x:v>
+        <x:v>1231</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>63674</x:v>
+        <x:v>71764</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>38701</x:v>
+        <x:v>40201</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1231</x:v>
+        <x:v>1261</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>71764</x:v>
+        <x:v>73294</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>40201</x:v>
+        <x:v>41701</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1261</x:v>
+        <x:v>1291</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>73294</x:v>
+        <x:v>74824</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>41701</x:v>
+        <x:v>42421</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1291</x:v>
+        <x:v>1321</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>74824</x:v>
+        <x:v>75574</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>13230</x:v>
+        <x:v>15030</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>42421</x:v>
+        <x:v>43921</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>13230</x:v>
+        <x:v>15030</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1321</x:v>
+        <x:v>1381</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>75574</x:v>
+        <x:v>80734</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>15030</x:v>
+        <x:v>13230</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>43921</x:v>
+        <x:v>44641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>15030</x:v>
+        <x:v>13230</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1381</x:v>
+        <x:v>1411</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>80734</x:v>
+        <x:v>77884</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>44641</x:v>
+        <x:v>45361</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1411</x:v>
+        <x:v>1441</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>77884</x:v>
+        <x:v>78634</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>45361</x:v>
+        <x:v>46081</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1441</x:v>
+        <x:v>1471</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>78634</x:v>
+        <x:v>79384</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>13230</x:v>
+        <x:v>13730</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>46081</x:v>
+        <x:v>47581</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>13230</x:v>
+        <x:v>13730</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1471</x:v>
+        <x:v>1501</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>79384</x:v>
+        <x:v>81914</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>47581</x:v>
+        <x:v>49741</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1501</x:v>
+        <x:v>1531</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>81914</x:v>
+        <x:v>84104</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>49741</x:v>
+        <x:v>56461</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1531</x:v>
+        <x:v>1681</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>84104</x:v>
+        <x:v>90974</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>56461</x:v>
+        <x:v>59401</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1681</x:v>
+        <x:v>1771</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>90974</x:v>
+        <x:v>94004</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>59401</x:v>
+        <x:v>61561</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1771</x:v>
+        <x:v>1861</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>94004</x:v>
+        <x:v>96254</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>61561</x:v>
+        <x:v>63061</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1861</x:v>
+        <x:v>1891</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>96254</x:v>
+        <x:v>97784</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>63061</x:v>
+        <x:v>66061</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1891</x:v>
+        <x:v>1951</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>97784</x:v>
+        <x:v>100844</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>66061</x:v>
+        <x:v>67561</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1951</x:v>
+        <x:v>1981</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>100844</x:v>
+        <x:v>102374</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>67561</x:v>
+        <x:v>69061</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1981</x:v>
+        <x:v>2011</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>102374</x:v>
+        <x:v>103904</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>69061</x:v>
+        <x:v>72061</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2011</x:v>
+        <x:v>2071</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>103904</x:v>
+        <x:v>106964</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>4436</x:v>
+        <x:v>5636</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>13730</x:v>
+        <x:v>15890</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>13730</x:v>
+        <x:v>15890</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2071</x:v>
+        <x:v>2131</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>106964</x:v>
+        <x:v>112544</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>72061</x:v>
+        <x:v>74941</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2131</x:v>
+        <x:v>2191</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>112544</x:v>
+        <x:v>115484</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>15890</x:v>
+        <x:v>16390</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>74941</x:v>
+        <x:v>80941</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>15890</x:v>
+        <x:v>16390</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2191</x:v>
+        <x:v>2251</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>115484</x:v>
+        <x:v>122544</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>80941</x:v>
+        <x:v>86941</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2251</x:v>
+        <x:v>2341</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>122544</x:v>
+        <x:v>128634</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>16390</x:v>
+        <x:v>16890</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>86941</x:v>
+        <x:v>97441</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>16390</x:v>
+        <x:v>16890</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2341</x:v>
+        <x:v>2491</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>128634</x:v>
+        <x:v>140284</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>97441</x:v>
+        <x:v>98161</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2491</x:v>
+        <x:v>2521</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>140284</x:v>
+        <x:v>141034</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>16890</x:v>
+        <x:v>17070</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>98161</x:v>
+        <x:v>98881</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>16890</x:v>
+        <x:v>17070</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2521</x:v>
+        <x:v>2551</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>141034</x:v>
+        <x:v>142144</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>17070</x:v>
+        <x:v>17570</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>98881</x:v>
+        <x:v>100381</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>17070</x:v>
+        <x:v>17570</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2551</x:v>
+        <x:v>2581</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>142144</x:v>
+        <x:v>144674</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>100381</x:v>
+        <x:v>101881</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2581</x:v>
+        <x:v>2611</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>144674</x:v>
+        <x:v>146204</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>101881</x:v>
+        <x:v>104881</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2611</x:v>
+        <x:v>2671</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>146204</x:v>
+        <x:v>149264</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>104881</x:v>
+        <x:v>119881</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2671</x:v>
+        <x:v>2971</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>149264</x:v>
+        <x:v>164564</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>17570</x:v>
+        <x:v>19730</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>119881</x:v>
+        <x:v>121381</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>17570</x:v>
+        <x:v>19730</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2971</x:v>
+        <x:v>3001</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>164564</x:v>
+        <x:v>171914</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>19730</x:v>
+        <x:v>22730</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>121381</x:v>
+        <x:v>133381</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>19730</x:v>
+        <x:v>22730</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3001</x:v>
+        <x:v>3181</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>171914</x:v>
+        <x:v>190094</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>22730</x:v>
+        <x:v>23230</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>133381</x:v>
+        <x:v>134881</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>22730</x:v>
+        <x:v>23230</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3181</x:v>
+        <x:v>3211</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>190094</x:v>
+        <x:v>192624</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>134881</x:v>
+        <x:v>136381</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3211</x:v>
+        <x:v>3241</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>192624</x:v>
+        <x:v>194154</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>23230</x:v>
+        <x:v>25030</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>23230</x:v>
+        <x:v>25030</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3241</x:v>
+        <x:v>3271</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>194154</x:v>
+        <x:v>197784</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>25030</x:v>
+        <x:v>23230</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>25030</x:v>
+        <x:v>23230</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>197784</x:v>
+        <x:v>194184</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>23230</x:v>
+        <x:v>23410</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>136381</x:v>
+        <x:v>143101</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>23230</x:v>
+        <x:v>23410</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3271</x:v>
+        <x:v>3361</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>194184</x:v>
+        <x:v>201354</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5636</x:v>
+        <x:v>8516</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>23410</x:v>
+        <x:v>28810</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>23410</x:v>
+        <x:v>28810</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3361</x:v>
+        <x:v>3391</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>201354</x:v>
+        <x:v>215064</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>28810</x:v>
+        <x:v>29310</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>143101</x:v>
+        <x:v>149101</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>28810</x:v>
+        <x:v>29310</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3391</x:v>
+        <x:v>3451</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>215064</x:v>
+        <x:v>222124</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>29310</x:v>
+        <x:v>29810</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>149101</x:v>
+        <x:v>153601</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>29310</x:v>
+        <x:v>29810</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3451</x:v>
+        <x:v>3481</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>222124</x:v>
+        <x:v>227654</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>153601</x:v>
+        <x:v>158101</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3481</x:v>
+        <x:v>3571</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>227654</x:v>
+        <x:v>232244</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>158101</x:v>
+        <x:v>162601</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3571</x:v>
+        <x:v>3601</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>232244</x:v>
+        <x:v>236774</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>162601</x:v>
+        <x:v>160261</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>236774</x:v>
+        <x:v>234434</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>29810</x:v>
+        <x:v>30310</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>160261</x:v>
+        <x:v>161761</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>29810</x:v>
+        <x:v>30310</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3601</x:v>
+        <x:v>3631</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>234434</x:v>
+        <x:v>236964</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>161761</x:v>
+        <x:v>167761</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3631</x:v>
+        <x:v>3751</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>236964</x:v>
+        <x:v>243084</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>167761</x:v>
+        <x:v>177521</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3751</x:v>
+        <x:v>3991</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>243084</x:v>
+        <x:v>253084</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>30310</x:v>
+        <x:v>30810</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>177521</x:v>
+        <x:v>179021</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>30310</x:v>
+        <x:v>30810</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3991</x:v>
+        <x:v>4021</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>253084</x:v>
+        <x:v>255614</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>30810</x:v>
+        <x:v>30310</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>30810</x:v>
+        <x:v>30310</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>255614</x:v>
+        <x:v>254614</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>179021</x:v>
+        <x:v>180521</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4021</x:v>
+        <x:v>4051</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>254614</x:v>
+        <x:v>256144</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>180521</x:v>
+        <x:v>182021</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4051</x:v>
+        <x:v>4081</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>256144</x:v>
+        <x:v>257674</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>182021</x:v>
+        <x:v>186521</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4081</x:v>
+        <x:v>4111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>257674</x:v>
+        <x:v>262204</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>186521</x:v>
+        <x:v>188681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4111</x:v>
+        <x:v>4141</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>262204</x:v>
+        <x:v>264394</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>188681</x:v>
+        <x:v>192401</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4141</x:v>
+        <x:v>4231</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>264394</x:v>
+        <x:v>268204</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>192401</x:v>
+        <x:v>193901</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4231</x:v>
+        <x:v>4261</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>268204</x:v>
+        <x:v>269734</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:X.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:X.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>8516</x:v>
+        <x:v>8566</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>4261</x:v>
+        <x:v>4291</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>269734</x:v>
+        <x:v>269814</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">
